--- a/data/trans_dic/P6903-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Clase-trans_dic.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,77; 35,65</t>
+          <t>14,95; 36,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,84; 34,8</t>
+          <t>12,28; 34,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20,53; 50,48</t>
+          <t>19,98; 50,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19,53; 47,9</t>
+          <t>18,72; 46,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 37,05</t>
+          <t>13,48; 37,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,97; 40,42</t>
+          <t>12,2; 38,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,72; 62,48</t>
+          <t>31,38; 62,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,79; 57,28</t>
+          <t>35,75; 57,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,98; 32,44</t>
+          <t>16,61; 32,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 33,62</t>
+          <t>14,95; 32,61</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31,11; 52,14</t>
+          <t>30,19; 51,91</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,56; 50,02</t>
+          <t>31,24; 49,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 37,53</t>
+          <t>10,92; 37,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,13; 43,73</t>
+          <t>13,77; 43,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,04; 59,02</t>
+          <t>23,53; 60,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,49; 36,78</t>
+          <t>12,7; 37,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,98; 33,11</t>
+          <t>7,79; 31,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,4; 34,31</t>
+          <t>3,43; 31,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 51,37</t>
+          <t>17,68; 50,72</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,93; 39,62</t>
+          <t>17,02; 41,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,08; 30,12</t>
+          <t>12,55; 30,08</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,3; 31,84</t>
+          <t>12,7; 33,0</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24,7; 50,13</t>
+          <t>23,62; 50,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,66; 35,39</t>
+          <t>16,69; 34,6</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,97; 46,93</t>
+          <t>26,18; 47,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,88; 33,0</t>
+          <t>13,24; 31,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23,87; 47,97</t>
+          <t>25,19; 48,56</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,47; 51,06</t>
+          <t>20,38; 49,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,2; 56,89</t>
+          <t>10,5; 57,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,46; 56,81</t>
+          <t>22,23; 58,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,27; 89,62</t>
+          <t>22,63; 89,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,56; 56,99</t>
+          <t>19,09; 55,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,75; 46,4</t>
+          <t>25,86; 44,31</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,17; 37,49</t>
+          <t>19,29; 36,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,88; 52,62</t>
+          <t>27,95; 49,77</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,22; 46,94</t>
+          <t>22,7; 47,77</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,06</t>
+          <t>26,18; 39,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,28; 30,97</t>
+          <t>15,11; 31,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,41; 49,56</t>
+          <t>32,37; 50,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,02; 46,37</t>
+          <t>28,28; 46,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 46,27</t>
+          <t>19,76; 45,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,58; 54,69</t>
+          <t>29,41; 54,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,85; 48,94</t>
+          <t>27,18; 48,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,38; 47,5</t>
+          <t>31,22; 47,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27,12; 38,73</t>
+          <t>26,58; 38,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,34; 36,96</t>
+          <t>23,05; 37,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,18; 47,35</t>
+          <t>33,17; 46,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,89; 44,81</t>
+          <t>31,96; 44,72</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 48,14</t>
+          <t>22,72; 47,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,12; 46,26</t>
+          <t>17,44; 46,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27,78; 53,0</t>
+          <t>28,02; 51,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27,41; 55,06</t>
+          <t>26,29; 56,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,22; 56,07</t>
+          <t>31,61; 55,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,16; 59,67</t>
+          <t>27,21; 58,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,6; 59,81</t>
+          <t>31,3; 59,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,49; 56,15</t>
+          <t>16,85; 56,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,48; 48,66</t>
+          <t>30,56; 48,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,54; 48,17</t>
+          <t>26,92; 49,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32,68; 51,44</t>
+          <t>32,09; 51,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,44; 51,73</t>
+          <t>19,99; 51,34</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1349,62 +1349,62 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>41,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -1417,221 +1417,80 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,44; 36,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,51; 28,94</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>33,63; 44,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,56; 39,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,95; 36,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,64; 41,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>34,33; 47,98</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,3; 45,15</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>27,74; 35,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>24,0; 32,52</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>35,78; 44,41</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>30,45; 40,98</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>31,59%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>23,83%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>38,84%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>34,19%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,78%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>34,69%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>38,76%</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>31,33%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>36,53%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>27,29; 36,11</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>19,21; 28,57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>33,68; 44,25</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>28,69; 40,75</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>25,09; 37,85</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28,46; 41,47</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,45; 48,95</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>28,34; 44,61</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>27,76; 35,01</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>24,5; 32,35</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35,71; 44,29</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>30,28; 40,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="K1:N1"/>
@@ -1647,7 +1506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1669,7 +1528,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas</t>
+          <t>Población que su trabajo le afecta de manera que se siente agotado a todas horas (tasa de respuesta: 99,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9616; 23202</t>
+          <t>9732; 23712</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6566; 19297</t>
+          <t>6810; 19277</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9629; 23679</t>
+          <t>9373; 23651</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8947; 21948</t>
+          <t>8576; 21262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6156; 17282</t>
+          <t>6290; 17647</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6128; 17732</t>
+          <t>5351; 16945</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14571; 28700</t>
+          <t>14412; 28503</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20392; 33574</t>
+          <t>20955; 33621</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18972; 36250</t>
+          <t>18558; 36238</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>15306; 33393</t>
+          <t>14852; 32395</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28886; 48409</t>
+          <t>28028; 48194</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32952; 52238</t>
+          <t>32621; 51910</t>
         </is>
       </c>
     </row>
@@ -2135,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4934; 15896</t>
+          <t>4625; 15834</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5134; 15891</t>
+          <t>5005; 15697</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6967; 17846</t>
+          <t>7114; 18307</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6235; 18360</t>
+          <t>6338; 18535</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3320; 13781</t>
+          <t>3240; 13194</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>906; 9131</t>
+          <t>914; 8343</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5468; 15098</t>
+          <t>5196; 14910</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6716; 16703</t>
+          <t>7174; 17553</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10146; 25290</t>
+          <t>10542; 25260</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7745; 20045</t>
+          <t>7998; 20778</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14729; 29893</t>
+          <t>14084; 29991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16262; 32583</t>
+          <t>15369; 31857</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26981; 46945</t>
+          <t>26191; 47430</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10874; 25857</t>
+          <t>10369; 25008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15965; 32090</t>
+          <t>16848; 32482</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11611; 28968</t>
+          <t>11563; 28023</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1173; 9265</t>
+          <t>1711; 9348</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7236; 19159</t>
+          <t>7495; 19723</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2131; 8576</t>
+          <t>2166; 8561</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3311; 10166</t>
+          <t>3406; 9988</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31111; 53975</t>
+          <t>30075; 51545</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>22601; 42009</t>
+          <t>21620; 41152</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21316; 40235</t>
+          <t>21369; 38053</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17314; 35002</t>
+          <t>16928; 35624</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52535; 80452</t>
+          <t>52569; 78832</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17438; 35355</t>
+          <t>17249; 36453</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44363; 67830</t>
+          <t>44298; 68776</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37321; 61768</t>
+          <t>37669; 62372</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9991; 23110</t>
+          <t>9871; 22586</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19758; 36535</t>
+          <t>19645; 36119</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24260; 41144</t>
+          <t>22851; 40771</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33189; 50238</t>
+          <t>33018; 49953</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>67998; 97118</t>
+          <t>66663; 95716</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>42238; 66887</t>
+          <t>41713; 67508</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73310; 104620</t>
+          <t>73287; 103447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76217; 107088</t>
+          <t>76382; 106875</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2618,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14786; 30816</t>
+          <t>14544; 30454</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6847; 18508</t>
+          <t>6977; 18708</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19193; 36622</t>
+          <t>19360; 35399</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14026; 28173</t>
+          <t>13452; 28741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20491; 36792</t>
+          <t>20740; 36680</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12295; 26057</t>
+          <t>11884; 25639</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14482; 28306</t>
+          <t>14811; 28145</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>22255; 71448</t>
+          <t>21438; 71950</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39512; 63076</t>
+          <t>39611; 63236</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22206; 40306</t>
+          <t>22525; 41355</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>38043; 59888</t>
+          <t>37359; 59735</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>38253; 92297</t>
+          <t>35659; 91601</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2831,62 +2690,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>108</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>194</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>205</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>302</t>
         </is>
       </c>
     </row>
@@ -2899,62 +2758,62 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>149217</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>77275</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>135950</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>115185</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>67753</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>74473</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89846</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>136291</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>216970</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>151748</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>225796</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>251476</t>
         </is>
       </c>
     </row>
@@ -2967,282 +2826,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>129613; 170683</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>63279; 93865</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>117715; 156230</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>96204; 133498</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>54919; 81376</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>61476; 88549</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>74264; 103788</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>95989; 158735</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>192104; 242897</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>129351; 175264</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>202638; 251475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>209604; 282100</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>302</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>149217</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>77275</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>135950</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>115185</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>67753</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>74473</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>89846</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>136291</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>216970</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>151748</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>225796</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>251476</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>128890; 170546</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>62308; 92651</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>117870; 154859</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>96638; 137275</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>55237; 83314</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>61107; 89027</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>76669; 105873</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>99642; 156868</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>192224; 242444</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>132031; 174382</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>202214; 250839</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>208444; 278417</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="10">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
@@ -3252,7 +2903,6 @@
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="K1:N1"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P6903-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P6903-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 36,43</t>
+          <t>14,06; 36,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,28; 34,76</t>
+          <t>12,06; 36,42</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19,98; 50,42</t>
+          <t>21,59; 52,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18,72; 46,41</t>
+          <t>20,56; 51,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,48; 37,83</t>
+          <t>13,59; 38,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,2; 38,63</t>
+          <t>13,65; 40,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,38; 62,05</t>
+          <t>33,12; 61,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>35,75; 57,37</t>
+          <t>34,48; 56,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,61; 32,43</t>
+          <t>16,7; 32,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,95; 32,61</t>
+          <t>15,81; 33,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,19; 51,91</t>
+          <t>30,27; 50,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>31,24; 49,71</t>
+          <t>30,85; 49,11</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 37,38</t>
+          <t>11,46; 39,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 43,19</t>
+          <t>13,55; 44,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,53; 60,55</t>
+          <t>22,1; 59,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 37,13</t>
+          <t>12,37; 37,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,79; 31,7</t>
+          <t>8,1; 33,18</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 31,35</t>
+          <t>3,58; 35,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,68; 50,72</t>
+          <t>18,91; 53,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,02; 41,64</t>
+          <t>18,65; 42,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,55; 30,08</t>
+          <t>12,25; 28,83</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12,7; 33,0</t>
+          <t>12,51; 33,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23,62; 50,29</t>
+          <t>26,25; 51,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,69; 34,6</t>
+          <t>17,21; 34,78</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,27 +964,27 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
+          <t>35,95%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>35,24%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>27,08%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>38,79%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>36,37%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>35,24%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>27,08%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>33,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 47,42</t>
+          <t>27,0; 47,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13,24; 31,92</t>
+          <t>13,69; 32,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25,19; 48,56</t>
+          <t>24,54; 47,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20,38; 49,4</t>
+          <t>21,75; 51,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,5; 57,39</t>
+          <t>7,29; 57,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22,23; 58,49</t>
+          <t>21,47; 58,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,63; 89,47</t>
+          <t>22,82; 89,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 55,99</t>
+          <t>21,08; 55,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,86; 44,31</t>
+          <t>26,17; 44,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,29; 36,72</t>
+          <t>18,96; 36,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>27,95; 49,77</t>
+          <t>27,91; 51,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>22,7; 47,77</t>
+          <t>25,45; 49,48</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>40,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>26,18; 39,25</t>
+          <t>26,05; 39,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 31,93</t>
+          <t>15,7; 31,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>32,37; 50,25</t>
+          <t>32,07; 49,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,28; 46,82</t>
+          <t>31,76; 50,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,76; 45,22</t>
+          <t>20,01; 45,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 54,07</t>
+          <t>29,43; 54,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,18; 48,49</t>
+          <t>27,04; 49,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,22; 47,23</t>
+          <t>32,27; 47,92</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26,58; 38,17</t>
+          <t>26,56; 39,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,05; 37,31</t>
+          <t>23,27; 37,09</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,17; 46,82</t>
+          <t>32,76; 46,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>31,96; 44,72</t>
+          <t>34,2; 46,99</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>44,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>22,72; 47,58</t>
+          <t>22,81; 48,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 46,77</t>
+          <t>15,97; 48,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>28,02; 51,23</t>
+          <t>28,89; 51,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26,29; 56,17</t>
+          <t>23,57; 48,97</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>31,61; 55,89</t>
+          <t>30,8; 56,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,21; 58,71</t>
+          <t>27,73; 59,59</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,3; 59,47</t>
+          <t>32,0; 59,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>16,85; 56,54</t>
+          <t>41,16; 58,92</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30,56; 48,78</t>
+          <t>30,53; 48,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,92; 49,43</t>
+          <t>25,62; 47,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32,09; 51,31</t>
+          <t>32,98; 51,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,99; 51,34</t>
+          <t>37,04; 52,59</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>39,01%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>27,44; 36,14</t>
+          <t>27,22; 35,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,51; 28,94</t>
+          <t>19,38; 28,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33,63; 44,64</t>
+          <t>33,49; 44,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>28,56; 39,63</t>
+          <t>30,58; 41,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>24,95; 36,97</t>
+          <t>25,12; 37,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,64; 41,25</t>
+          <t>27,66; 41,32</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>34,33; 47,98</t>
+          <t>34,78; 48,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27,3; 45,15</t>
+          <t>37,73; 46,64</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>27,74; 35,08</t>
+          <t>27,72; 34,98</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,0; 32,52</t>
+          <t>24,38; 32,36</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,78; 44,41</t>
+          <t>35,89; 44,44</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>30,45; 40,98</t>
+          <t>35,48; 42,64</t>
         </is>
       </c>
     </row>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1753,7 +1753,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>27184</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41616</t>
+          <t>45475</t>
         </is>
       </c>
     </row>
@@ -1786,62 +1786,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9732; 23712</t>
+          <t>9148; 23748</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6810; 19277</t>
+          <t>6686; 20198</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9373; 23651</t>
+          <t>10128; 24505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8576; 21262</t>
+          <t>10698; 26630</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6290; 17647</t>
+          <t>6340; 18161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5351; 16945</t>
+          <t>5988; 17648</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14412; 28503</t>
+          <t>15213; 28269</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20955; 33621</t>
+          <t>21144; 34490</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18558; 36238</t>
+          <t>18660; 36077</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14852; 32395</t>
+          <t>15708; 33030</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28028; 48194</t>
+          <t>28108; 47238</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32621; 51910</t>
+          <t>34976; 55671</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11656</t>
+          <t>11709</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>25031</t>
         </is>
       </c>
     </row>
@@ -1994,62 +1994,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4625; 15834</t>
+          <t>4855; 16792</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5005; 15697</t>
+          <t>4924; 16013</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7114; 18307</t>
+          <t>6683; 18100</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6338; 18535</t>
+          <t>6324; 18919</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3240; 13194</t>
+          <t>3372; 13808</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>914; 8343</t>
+          <t>953; 9392</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5196; 14910</t>
+          <t>5558; 15675</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7174; 17553</t>
+          <t>8477; 19094</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10542; 25260</t>
+          <t>10283; 24212</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7998; 20778</t>
+          <t>7877; 20927</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14084; 29991</t>
+          <t>15651; 30859</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15369; 31857</t>
+          <t>16618; 33585</t>
         </is>
       </c>
     </row>
@@ -2149,7 +2149,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>21753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7355</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2189,7 +2189,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25318</t>
+          <t>29108</t>
         </is>
       </c>
     </row>
@@ -2202,62 +2202,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>26191; 47430</t>
+          <t>27012; 47067</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10369; 25008</t>
+          <t>10723; 25426</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16848; 32482</t>
+          <t>16412; 31865</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11563; 28023</t>
+          <t>12957; 30852</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1711; 9348</t>
+          <t>1188; 9435</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7495; 19723</t>
+          <t>7240; 19699</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2166; 8561</t>
+          <t>2184; 8605</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3406; 9988</t>
+          <t>4312; 11326</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>30075; 51545</t>
+          <t>30439; 52058</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21620; 41152</t>
+          <t>21252; 40602</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21369; 38053</t>
+          <t>21342; 39204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16928; 35624</t>
+          <t>20366; 39599</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49610</t>
+          <t>62639</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>41014</t>
+          <t>45465</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2397,7 +2397,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90624</t>
+          <t>108104</t>
         </is>
       </c>
     </row>
@@ -2410,62 +2410,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>52569; 78832</t>
+          <t>52320; 79954</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17249; 36453</t>
+          <t>17928; 36025</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44298; 68776</t>
+          <t>43894; 67560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37669; 62372</t>
+          <t>48842; 76954</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9871; 22586</t>
+          <t>9996; 22814</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19645; 36119</t>
+          <t>19662; 36161</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>22851; 40771</t>
+          <t>22736; 41468</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>33018; 49953</t>
+          <t>36711; 54521</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>66663; 95716</t>
+          <t>66613; 98187</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41713; 67508</t>
+          <t>42104; 67126</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73287; 103447</t>
+          <t>72389; 102256</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76382; 106875</t>
+          <t>91489; 125700</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2565,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20657</t>
+          <t>24204</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2585,7 +2585,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>49724</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>70380</t>
+          <t>75048</t>
         </is>
       </c>
     </row>
@@ -2618,62 +2618,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>14544; 30454</t>
+          <t>14603; 30931</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6977; 18708</t>
+          <t>6389; 19226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19360; 35399</t>
+          <t>19960; 35586</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>13452; 28741</t>
+          <t>15476; 32155</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>20740; 36680</t>
+          <t>20211; 37370</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11884; 25639</t>
+          <t>12110; 26023</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14811; 28145</t>
+          <t>15145; 27942</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21438; 71950</t>
+          <t>41840; 59891</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>39611; 63236</t>
+          <t>39576; 63088</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22525; 41355</t>
+          <t>21440; 39922</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37359; 59735</t>
+          <t>38399; 59833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>35659; 91601</t>
+          <t>61970; 87985</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>115185</t>
+          <t>137708</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>136291</t>
+          <t>145059</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>251476</t>
+          <t>282767</t>
         </is>
       </c>
     </row>
@@ -2826,62 +2826,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>129613; 170683</t>
+          <t>128558; 169966</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>63279; 93865</t>
+          <t>62856; 92954</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>117715; 156230</t>
+          <t>117232; 155947</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96204; 133498</t>
+          <t>116852; 160285</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>54919; 81376</t>
+          <t>55287; 82728</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>61476; 88549</t>
+          <t>59371; 88706</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>74264; 103788</t>
+          <t>75223; 104953</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>95989; 158735</t>
+          <t>129300; 159831</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>192104; 242897</t>
+          <t>191958; 242244</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>129351; 175264</t>
+          <t>131419; 174395</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>202638; 251475</t>
+          <t>203259; 251646</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>209604; 282100</t>
+          <t>257153; 309075</t>
         </is>
       </c>
     </row>
